--- a/MainTop/31.12.2025 имена/31.12.2025 имена.xlsx
+++ b/MainTop/31.12.2025 имена/31.12.2025 имена.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\31.12.2025 имена\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\31.12.2025 имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776B8739-29F2-47DD-ABB1-FE6DA6BFAC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBC5C7F-61BA-4F0B-BD5B-F85A82A655CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
